--- a/DualStageSystems.xlsx
+++ b/DualStageSystems.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{632ECB99-A995-4AF8-9FDB-291806B29DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F20D34-8A99-4FDB-BC4F-26F3194CF23F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -695,7 +695,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -755,21 +755,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -788,20 +799,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -883,6 +880,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1171,48 +1172,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="25" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="25"/>
+      <c r="N1" s="32"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="35" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="35" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -1230,7 +1231,7 @@
       <c r="K2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="39" t="s">
         <v>29</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -1239,28 +1240,28 @@
       <c r="N2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="32" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="25"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="35"/>
       <c r="C3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
       <c r="G3" s="6" t="s">
         <v>47</v>
       </c>
@@ -1276,25 +1277,25 @@
       <c r="K3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="34"/>
+      <c r="L3" s="39"/>
       <c r="M3" s="6" t="s">
         <v>58</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="O3" s="27"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
     </row>
     <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
@@ -1304,13 +1305,13 @@
         <v>54</v>
       </c>
       <c r="K4" s="11"/>
-      <c r="L4" s="35"/>
+      <c r="L4" s="40"/>
       <c r="M4" s="10"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -1411,78 +1412,78 @@
       <c r="R6" s="4"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="28">
         <v>300</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="29">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="29">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="38" t="s">
+      <c r="L7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="39">
+      <c r="M7" s="27">
         <v>9.75</v>
       </c>
-      <c r="N7" s="38"/>
-      <c r="O7" s="39" t="s">
+      <c r="N7" s="28"/>
+      <c r="O7" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="37" t="s">
+      <c r="P7" s="29" t="s">
         <v>31</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="R7" s="40"/>
-    </row>
-    <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="37"/>
+      <c r="R7" s="26"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="29"/>
       <c r="Q8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="R8" s="40"/>
+      <c r="R8" s="26"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
@@ -2772,8 +2773,8 @@
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
       <c r="L43" s="15"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="40"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="26"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
@@ -2792,8 +2793,8 @@
       <c r="J44" s="12"/>
       <c r="K44" s="12"/>
       <c r="L44" s="15"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="40"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="26"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
@@ -2812,8 +2813,8 @@
       <c r="J45" s="12"/>
       <c r="K45" s="12"/>
       <c r="L45" s="15"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="40"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="26"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
@@ -2834,8 +2835,8 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="22"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="40"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="26"/>
       <c r="O46" s="4"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
@@ -2854,8 +2855,8 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="22"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="40"/>
+      <c r="M47" s="25"/>
+      <c r="N47" s="26"/>
       <c r="O47" s="4"/>
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
@@ -2874,8 +2875,8 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="22"/>
-      <c r="M48" s="41"/>
-      <c r="N48" s="40"/>
+      <c r="M48" s="25"/>
+      <c r="N48" s="26"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
@@ -2883,17 +2884,15 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="L2:L4"/>
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="P2:P4"/>
     <mergeCell ref="Q2:Q4"/>
@@ -2910,15 +2909,17 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="D1:L1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/DualStageSystems.xlsx
+++ b/DualStageSystems.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{632ECB99-A995-4AF8-9FDB-291806B29DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F20D34-8A99-4FDB-BC4F-26F3194CF23F}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="5865" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -827,9 +827,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>213040</xdr:colOff>
+      <xdr:colOff>209230</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>169336</xdr:rowOff>
+      <xdr:rowOff>173146</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
